--- a/formulation/management/commands/Ingredients Name.xlsx
+++ b/formulation/management/commands/Ingredients Name.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\welcome\Desktop\JRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46B7E51-FEDA-4A8E-9F35-8529C4943563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E48763F-2FCA-4780-8434-639A9E2EF7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4890" yWindow="2810" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feed formulation New" sheetId="1" r:id="rId1"/>
@@ -4060,7 +4060,7 @@
         <v>23</v>
       </c>
       <c r="T36" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U36" s="2">
         <v>17</v>
